--- a/papers/Table I - Comparison.xlsx
+++ b/papers/Table I - Comparison.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\UVSQ\simulation_VLP\papers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\userlisv\Documents\Kevin\Journal simulations\simulation_VLP\papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE7E5A8-C9A6-4E98-AC18-3BA8AFA7010D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EBD2EF-5C1F-468D-9A50-62EB1FFC1427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="89">
   <si>
     <t>Work</t>
   </si>
@@ -190,9 +190,6 @@
   </si>
   <si>
     <t>5.9 (CDF_90%)</t>
-  </si>
-  <si>
-    <t>Power Ratio</t>
   </si>
   <si>
     <t>Positioning for optical wireless communications (OWC) has been the subject of
@@ -274,6 +271,165 @@
  or corner zones drop from 137.96 cm and 15.63 cm, to 38.34 cm
  and1.43cm,respectively, and the averaged positioning error of the
  whole room decreases from 11.97 cm to 1.74 cm.</t>
+  </si>
+  <si>
+    <t>High accuracy indoor visible light positioning using a long short term memory-fully connected network based algorithm</t>
+  </si>
+  <si>
+    <t>long short term memory-fully
+connected network</t>
+  </si>
+  <si>
+    <t>0.92 cm</t>
+  </si>
+  <si>
+    <t>1 LED / 3 tilted PD</t>
+  </si>
+  <si>
+    <t>1 x 1.1 x 1.75</t>
+  </si>
+  <si>
+    <t>In this work, a novel positioning algorithm based on a long short term memory-fully
+connected network (LSTM-FCN) is proposed to improve the performance of an indoor visible
+light positioning (VLP) system. Using the proposed LSTM-FCN based positioning algorithm,
+the VLP system with a single light emitting diode (LED) and multiple photodetectors (PDs) was
+implemented. On this basis, the positioning performance of the established VLP system using
+proposed LSTM-FCN, traditional FCN and support vector regression (SVR) based algorithm
+is investigated and compared. It is demonstrated that the VLP system using the proposed
+LSTM-FCN based algorithm has better performance than that using other machine learning
+algorithms. As a result, an average positioning error of 0.92 cm and a maximum positioning
+error of less than 5 cm can be obtained for the established VLP system.</t>
+  </si>
+  <si>
+    <t>4 x 4 x 3.1</t>
+  </si>
+  <si>
+    <t>6 x 6 x 3</t>
+  </si>
+  <si>
+    <t>3 x 3 x 2</t>
+  </si>
+  <si>
+    <t>1.5 x 1.5 x 1.5</t>
+  </si>
+  <si>
+    <t>5 x 5 x 3</t>
+  </si>
+  <si>
+    <t>0.5 x 0.5 x 0.3</t>
+  </si>
+  <si>
+    <t>4 x 4 x 2.5</t>
+  </si>
+  <si>
+    <t>4 x 5 x 5</t>
+  </si>
+  <si>
+    <t>5 x 5 x 4</t>
+  </si>
+  <si>
+    <t>With the rapid development of information technology, the application field of city positioning
+technology is more and more extensive. Traditional indoor positioning technology has shortcomings
+in positioning accuracy, equipment cost, security and so on. Visible light indoor positioning
+technology can effectively solve the above problems. This paper presents an Adaptive
+boosting- Bayes (A-Bayes) localization algorithm. In this algorithm, three tilted photodetectors
+and one horizontal PD are used as receivers to measure the received optical power of each PD and
+set up a fingerprint database. The Adaboost strong classifier is used to divide the test space into
+two regions: the center and the edge. In the online positioning stage, for the measured received
+optical power, the region to which it belongs is first determined, and then the Bayesian matching
+algorithm is used to match the regions to complete the positioning. The experimental results show
+that in the test space of, and the overall average positioning error is 9.27 cm. Compared with the
+traditional indoor positioning algorithm, the positioning error of the proposed algorithm is
+smaller; Compared with the traditional multi lamp location algorithm, the algorithm proposed in
+this paper avoids the interference between multi light source symbols, and the equipment is
+simpler; Compared with the traditional fingerprint matching algorithm, the proposed algorithm
+has faster positioning speed.</t>
+  </si>
+  <si>
+    <t>High precision indoor positioning algorithm of single LED lamp
+based on A-Bayes</t>
+  </si>
+  <si>
+    <t>9.27 cm</t>
+  </si>
+  <si>
+    <t>3 x 3 x 3</t>
+  </si>
+  <si>
+    <t>1 LED / 4 PD (1 horizontal + 3 Tilted)</t>
+  </si>
+  <si>
+    <t>Bayesian algorithm</t>
+  </si>
+  <si>
+    <t>With the rapid development of information technology, there is a growing demand for people in
+indoor location services.This paper proposes a novel high-precision indoor three-dimensional
+positioning algorithm for single light emitting diode (LED). By using three tilted photodetectors
+(PD)and one horizontal PD as receivers.Calculating the ratio of received optical power of the
+three tilted PDs to the horizontal PD respectively. According to the relationship of position between
+the PDs and the tilt angle, azimuth angle, placement angle of the tilted PD and other
+parameters, establish a mathematical relationship between the received optical power ratio and
+the receiver's three-dimensional coordinates, calculate the three-dimensional coordinates of the
+receiver at any position. The simulation results show that in the positioning area of
+1×1×1.5m3, when the inclination angle α is 25°, the azimuth angle difference θ is 90°, the
+placement angle ω1=0°, ω2=90°, ω3=180°, the distance r between the horizontal PD center and
+the tilted PD center is 1 cm, the positioning accuracy is better, the point with the positioning
+error within 3 cm accounts for 84 % of the total test points, and the average positioning error is
+2.52 cm. Compared with the traditional indoor positioning technology, the cost of the positioning
+technology used in this paper is greatly reduced, the positioning accuracy is significantly improved,
+and can get three-dimensional coordinates</t>
+  </si>
+  <si>
+    <t>1 X 1 X 1.5</t>
+  </si>
+  <si>
+    <t>Indoor visible light high precision three-dimensional positioning
+algorithm based on single LED lamp</t>
+  </si>
+  <si>
+    <t>2.52 cm</t>
+  </si>
+  <si>
+    <t>Model-based (Power Ratio)</t>
+  </si>
+  <si>
+    <t>Model-based (Geometrical Equations)</t>
+  </si>
+  <si>
+    <t>Ours</t>
+  </si>
+  <si>
+    <t>GLS</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>Indoor positioning system for single LED light based on deep residual shrinkage network</t>
+  </si>
+  <si>
+    <t>To enhance the indoor visible light positioning (VLP) system’s performance, this paper proposes a deep residual
+shrinkage network (DRSN)-based VLP system utilizing a single LED and multiple photodetectors. This neural
+network effectively resolves issues prevalent in the training phase of conventional neural networks, such as
+vanishing or exploding gradients, noise interference, and indistinct feature characterization, by incorporating
+residual learning, soft threshold functions, and an attention mechanism. This approach contributes to a more
+stable and efficient training process. Simulation results illustrate that the DRSN algorithm produces an average
+localization error of 1.02 cm, with a maximum error of 4.35 cm in a 3.6 m × 3.6 m × 3 m space. During the
+experimental phase, the average localization error remains below 6 cm, with 90% of the errors below 10 cm.
+Comparative analysis with alternative localization algorithms reveals the proposed method’s ability to achieve
+precise localization accuracy.</t>
+  </si>
+  <si>
+    <t>Deep Residual Shrinkage method</t>
+  </si>
+  <si>
+    <t>3.6 × 3.6 × 3.0</t>
+  </si>
+  <si>
+    <t>5.85 cm</t>
   </si>
 </sst>
 </file>
@@ -614,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -622,12 +778,14 @@
     <col min="3" max="4" width="22.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="2"/>
     <col min="6" max="6" width="22.5703125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="2"/>
-    <col min="9" max="9" width="111" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="12.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="10" max="10" width="111" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -650,79 +808,88 @@
         <v>13</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>32</v>
+        <v>76</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="F3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>22</v>
@@ -731,27 +898,30 @@
         <v>10</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J4" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>22</v>
@@ -760,27 +930,30 @@
         <v>10</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>22</v>
@@ -789,19 +962,22 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2024</v>
       </c>
@@ -818,27 +994,30 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J7" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2024</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>22</v>
@@ -847,49 +1026,209 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="H8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J8" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
